--- a/就業金卡/20260228國籍和領域統計報表.xlsx
+++ b/就業金卡/20260228國籍和領域統計報表.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrtbh\實驗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062148FB-665D-4B03-8087-9DE35AEF7179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF873EDE-9171-41F6-B0D6-8F1EF5474970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="國籍和領域分" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -42,12 +42,6 @@
     <t>教育</t>
   </si>
   <si>
-    <t>文化藝術</t>
-  </si>
-  <si>
-    <t>體育</t>
-  </si>
-  <si>
     <t>金融</t>
   </si>
   <si>
@@ -234,9 +228,6 @@
     <t>南非</t>
   </si>
   <si>
-    <t>南韓</t>
-  </si>
-  <si>
     <t>哈薩克</t>
   </si>
   <si>
@@ -430,6 +421,18 @@
   </si>
   <si>
     <t>總計</t>
+  </si>
+  <si>
+    <t>運動</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文化、藝術</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韓國</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -808,36 +811,36 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2" s="3">
         <v>9</v>
@@ -878,7 +881,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -919,7 +922,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -960,7 +963,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
@@ -1001,7 +1004,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3">
         <v>12</v>
@@ -1042,7 +1045,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
@@ -1083,7 +1086,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
@@ -1124,7 +1127,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -1165,7 +1168,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" s="3">
         <v>25</v>
@@ -1206,7 +1209,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" s="3">
         <v>78</v>
@@ -1247,7 +1250,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" s="3">
         <v>21</v>
@@ -1288,7 +1291,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -1329,7 +1332,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="3">
         <v>21</v>
@@ -1370,7 +1373,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15" s="3">
         <v>128</v>
@@ -1411,7 +1414,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -1452,7 +1455,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17" s="3">
         <v>0</v>
@@ -1493,7 +1496,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
@@ -1534,7 +1537,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B19" s="3">
         <v>2</v>
@@ -1575,7 +1578,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B20" s="3">
         <v>0</v>
@@ -1616,7 +1619,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B21" s="3">
         <v>1</v>
@@ -1657,7 +1660,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B22" s="3">
         <v>0</v>
@@ -1698,7 +1701,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
@@ -1739,7 +1742,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B24" s="3">
         <v>2</v>
@@ -1780,7 +1783,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B25" s="3">
         <v>2</v>
@@ -1821,7 +1824,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B26" s="3">
         <v>20</v>
@@ -1862,7 +1865,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B27" s="3">
         <v>1</v>
@@ -1903,7 +1906,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B28" s="3">
         <v>0</v>
@@ -1944,7 +1947,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B29" s="3">
         <v>1</v>
@@ -1985,7 +1988,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B30" s="3">
         <v>26</v>
@@ -2026,7 +2029,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B31" s="3">
         <v>252</v>
@@ -2067,7 +2070,7 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B32" s="3">
         <v>0</v>
@@ -2108,7 +2111,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B33" s="3">
         <v>0</v>
@@ -2149,7 +2152,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B34" s="3">
         <v>3</v>
@@ -2190,7 +2193,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B35" s="3">
         <v>23</v>
@@ -2231,7 +2234,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B36" s="3">
         <v>0</v>
@@ -2272,7 +2275,7 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B37" s="3">
         <v>4</v>
@@ -2313,7 +2316,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B38" s="3">
         <v>0</v>
@@ -2354,7 +2357,7 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B39" s="3">
         <v>0</v>
@@ -2395,7 +2398,7 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B40" s="3">
         <v>1</v>
@@ -2436,7 +2439,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B41" s="3">
         <v>3</v>
@@ -2477,7 +2480,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B42" s="3">
         <v>0</v>
@@ -2518,7 +2521,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B43" s="3">
         <v>1</v>
@@ -2559,7 +2562,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B44" s="3">
         <v>0</v>
@@ -2600,7 +2603,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B45" s="3">
         <v>0</v>
@@ -2641,7 +2644,7 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B46" s="3">
         <v>4</v>
@@ -2682,7 +2685,7 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B47" s="3">
         <v>7</v>
@@ -2723,7 +2726,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B48" s="3">
         <v>14</v>
@@ -2764,7 +2767,7 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B49" s="3">
         <v>110</v>
@@ -2805,7 +2808,7 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B50" s="3">
         <v>0</v>
@@ -2846,7 +2849,7 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B51" s="3">
         <v>7</v>
@@ -2887,7 +2890,7 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B52" s="3">
         <v>1</v>
@@ -2928,7 +2931,7 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B53" s="3">
         <v>0</v>
@@ -2969,7 +2972,7 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B54" s="3">
         <v>1</v>
@@ -3010,7 +3013,7 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B55" s="3">
         <v>43</v>
@@ -3051,7 +3054,7 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B56" s="3">
         <v>5</v>
@@ -3092,7 +3095,7 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="B57" s="3">
         <v>57</v>
@@ -3133,7 +3136,7 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B58" s="3">
         <v>4</v>
@@ -3174,7 +3177,7 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B59" s="3">
         <v>0</v>
@@ -3215,7 +3218,7 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B60" s="3">
         <v>1</v>
@@ -3256,7 +3259,7 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B61" s="3">
         <v>0</v>
@@ -3297,7 +3300,7 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B62" s="3">
         <v>1</v>
@@ -3338,7 +3341,7 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B63" s="3">
         <v>1050</v>
@@ -3379,7 +3382,7 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B64" s="3">
         <v>147</v>
@@ -3420,7 +3423,7 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B65" s="3">
         <v>199</v>
@@ -3461,7 +3464,7 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B66" s="3">
         <v>0</v>
@@ -3502,7 +3505,7 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B67" s="3">
         <v>1</v>
@@ -3543,7 +3546,7 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B68" s="3">
         <v>3</v>
@@ -3584,7 +3587,7 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B69" s="3">
         <v>6</v>
@@ -3625,7 +3628,7 @@
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B70" s="3">
         <v>2</v>
@@ -3666,7 +3669,7 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B71" s="3">
         <v>0</v>
@@ -3707,7 +3710,7 @@
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B72" s="3">
         <v>4</v>
@@ -3748,7 +3751,7 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B73" s="3">
         <v>0</v>
@@ -3789,7 +3792,7 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B74" s="3">
         <v>1</v>
@@ -3830,7 +3833,7 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B75" s="3">
         <v>11</v>
@@ -3871,7 +3874,7 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B76" s="3">
         <v>0</v>
@@ -3912,7 +3915,7 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B77" s="3">
         <v>0</v>
@@ -3953,7 +3956,7 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B78" s="3">
         <v>0</v>
@@ -3994,7 +3997,7 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B79" s="3">
         <v>11</v>
@@ -4035,7 +4038,7 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B80" s="3">
         <v>109</v>
@@ -4076,7 +4079,7 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B81" s="3">
         <v>0</v>
@@ -4117,7 +4120,7 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B82" s="3">
         <v>2</v>
@@ -4158,7 +4161,7 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B83" s="3">
         <v>0</v>
@@ -4199,7 +4202,7 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B84" s="3">
         <v>42</v>
@@ -4240,7 +4243,7 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B85" s="3">
         <v>0</v>
@@ -4281,7 +4284,7 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B86" s="3">
         <v>0</v>
@@ -4322,7 +4325,7 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B87" s="3">
         <v>0</v>
@@ -4363,7 +4366,7 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B88" s="3">
         <v>2</v>
@@ -4404,7 +4407,7 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B89" s="3">
         <v>1</v>
@@ -4445,7 +4448,7 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B90" s="3">
         <v>0</v>
@@ -4486,7 +4489,7 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B91" s="3">
         <v>24</v>
@@ -4527,7 +4530,7 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B92" s="3">
         <v>34</v>
@@ -4568,7 +4571,7 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B93" s="3">
         <v>0</v>
@@ -4609,7 +4612,7 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B94" s="3">
         <v>9</v>
@@ -4650,7 +4653,7 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B95" s="3">
         <v>1</v>
@@ -4691,7 +4694,7 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B96" s="3">
         <v>10</v>
@@ -4732,7 +4735,7 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B97" s="3">
         <v>141</v>
@@ -4773,7 +4776,7 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B98" s="3">
         <v>16</v>
@@ -4814,7 +4817,7 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B99" s="3">
         <v>22</v>
@@ -4855,7 +4858,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B100" s="3">
         <v>0</v>
@@ -4896,7 +4899,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B101" s="3">
         <v>28</v>
@@ -4937,7 +4940,7 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B102" s="3">
         <v>1</v>
@@ -4978,7 +4981,7 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B103" s="3">
         <v>0</v>
@@ -5019,7 +5022,7 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B104" s="3">
         <v>2</v>
@@ -5060,7 +5063,7 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B105" s="3">
         <v>0</v>
@@ -5101,7 +5104,7 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B106" s="3">
         <v>8</v>
@@ -5142,7 +5145,7 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B107" s="3">
         <v>1</v>
@@ -5183,7 +5186,7 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B108" s="3">
         <v>82</v>
@@ -5224,7 +5227,7 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B109" s="3">
         <v>0</v>
@@ -5265,7 +5268,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B110" s="3">
         <v>0</v>
@@ -5306,7 +5309,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B111" s="3">
         <v>1</v>
@@ -5347,7 +5350,7 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B112" s="3">
         <v>6</v>
@@ -5388,7 +5391,7 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B113" s="3">
         <v>1</v>
@@ -5429,7 +5432,7 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B114" s="3">
         <v>3</v>
@@ -5470,7 +5473,7 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B115" s="3">
         <v>56</v>
@@ -5511,7 +5514,7 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B116" s="3">
         <v>4</v>
@@ -5552,7 +5555,7 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B117" s="3">
         <v>0</v>
@@ -5593,7 +5596,7 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B118" s="3">
         <v>0</v>
@@ -5634,7 +5637,7 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B119" s="3">
         <v>0</v>
@@ -5675,7 +5678,7 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B120" s="3">
         <v>10</v>
@@ -5716,7 +5719,7 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B121" s="3">
         <v>0</v>
@@ -5757,7 +5760,7 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B122" s="3">
         <v>2968</v>
